--- a/public/share/Etienne-Players.xlsx
+++ b/public/share/Etienne-Players.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,27 +29,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="FF666666"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +45,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A1A1A"/>
+        <fgColor rgb="001A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F4EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E0B0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,36 +67,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,20 +453,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
@@ -491,32 +477,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Perfume Match</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Challenge</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Played At (Kuwait)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Played At (UTC)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Entry ID</t>
         </is>
       </c>
     </row>
@@ -526,35 +502,25 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>@saalosaimi_</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1221</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
+          <t>@navyfade</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>navyfade</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1235</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 20:09</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 17:09</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>4cf52058-715f-4e21-9770-84b11a93ee6d</t>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03  23:19</t>
         </is>
       </c>
     </row>
@@ -564,35 +530,25 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>@aalwo_</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1192</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
+          <t>@saalosaimi_</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>saalosaimi_</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1221</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 20:41</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 17:41</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>21fb9dd4-3999-4ed0-80d6-1aca524ddc44</t>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:09</t>
         </is>
       </c>
     </row>
@@ -602,529 +558,613 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>@aalwo_</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>aalwo_</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>@bibii010101</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bibii010101</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wild Cotton</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  23:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
           <t>@hhzubaid</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>hhzubaid</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>1048</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 20:35</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 17:35</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>15880584-2668-4f7e-a909-8135a8827447</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>@salfajji</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>salfajji</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>850</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 20:13</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 17:13</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>299ab5c9-fc75-4e59-aca0-0bf6913c5cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>@icu96_</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>icu96_</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>832</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 18:32</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 15:32</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>a06f07f9-9cb0-4487-84ad-7ae5140d5ea8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>@eng_menawer</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>eng_menawer</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>813</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 18:52</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 15:52</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>ce7137e1-dbad-4c3b-9f17-aef6c5b4be6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>@farahpunzel</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>farahpunzel</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>799</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04  12:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>@bbritto99</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bbritto99</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>798</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04  00:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>@w1nb</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>w1nb</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>773</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04  06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>@aminaonthemat</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>aminaonthemat</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>wild-cotton</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 19:16</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 16:16</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>c65c365a-a026-41c6-a7b1-ab17b4324f2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Wild Cotton</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  19:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>@kjalabdul</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>kjalabdul</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>722</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>linen</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 21:44</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 18:44</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>d16fe713-ec0a-42b0-bd99-5e2d71c2340f</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Linen</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  21:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>@badoraaals</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>badoraaals</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>697</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 21:06</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 18:06</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>0a86b682-a7d5-4464-b115-c2950b18f9c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>@m_alwazzan88</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>m_alwazzan88</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>684</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>linen</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 22:57</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 19:57</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>89d6c385-52d1-4554-a074-b90d409e3c2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Linen</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>@ghazitark</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ghazitark</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>627</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 22:45</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 19:45</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>8b988e45-a508-41f1-bb76-8e99153b1aa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  22:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>@sonanddark</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>sonanddark</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>590</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 18:37</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 15:37</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>12fa2c91-64b9-4d83-861a-d4ba2d216b15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  18:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>@falnaqeeb</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>falnaqeeb</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>590</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>river</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 20:12</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 17:12</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>183ebcb6-1a89-47c8-a3c9-704c457b7061</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>River</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>@rydeenn</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>rydeenn</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
         <v>516</v>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 18:43</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 15:43</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>83a4fd9c-3f17-4c7b-9889-476b9f0bdfbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>@aminaxsalim</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>aminaxsalim</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>488</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 19:13</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 16:13</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>0c04c2a4-80b0-44f7-a654-73ba70aa550f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  19:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>@mfalhaaa</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>mfalhaaa</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>453</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  23:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>@salemalharan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>salemalharan</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04  02:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>@v97o0</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>v97o0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04  06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>@Jaljaiedan</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jaljaiedan</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>359</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 20:15</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-03 17:15</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>4e5c0f97-2bfb-432a-a659-a5a658c7e983</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:15</t>
         </is>
       </c>
     </row>
@@ -1139,51 +1179,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Etienne Game — Player Stats</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Snapshot taken 2026-05-03 23:00 Kuwait time</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total players</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Total players</t>
+          <t>Top score</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Highest score</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1221</v>
+          <t>Top player</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>@navyfade</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lowest score (on board)</t>
+          <t>Lowest score</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1197,53 +1247,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>748.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Perfume match distribution</t>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Snapshot taken</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-04  13:42  Kuwait</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>etienne</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>12</v>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wild-cotton</t>
+          <t>Wild Cotton</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>Linen</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>River</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>1</v>
       </c>
     </row>

--- a/public/share/Etienne-Players.xlsx
+++ b/public/share/Etienne-Players.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -642,16 +642,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>@salfajji</t>
+          <t>@zabzyy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>salfajji</t>
+          <t>zabzyy</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>850</v>
+        <v>1031</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  20:13</t>
+          <t>2026-05-05  16:07</t>
         </is>
       </c>
     </row>
@@ -670,16 +670,16 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>@icu96_</t>
+          <t>@noor11_09</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>icu96_</t>
+          <t>noor11_09</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>832</v>
+        <v>965</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03  18:32</t>
+          <t>2026-05-04  23:22</t>
         </is>
       </c>
     </row>
@@ -698,25 +698,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>@eng_menawer</t>
+          <t>@abdullahaljarki</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eng_menawer</t>
+          <t>abdullahaljarki</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>813</v>
+        <v>947</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>River</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  18:52</t>
+          <t>2026-05-05  17:54</t>
         </is>
       </c>
     </row>
@@ -726,16 +726,16 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>@farahpunzel</t>
+          <t>@farahmorad</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>farahpunzel</t>
+          <t>farahmorad</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>799</v>
+        <v>895</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04  12:23</t>
+          <t>2026-05-05  07:48</t>
         </is>
       </c>
     </row>
@@ -754,16 +754,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>@bbritto99</t>
+          <t>@salfajji</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bbritto99</t>
+          <t>salfajji</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>798</v>
+        <v>850</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04  00:06</t>
+          <t>2026-05-03  20:13</t>
         </is>
       </c>
     </row>
@@ -782,16 +782,16 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>@w1nb</t>
+          <t>@icu96_</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>w1nb</t>
+          <t>icu96_</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04  06:05</t>
+          <t>2026-05-03  18:32</t>
         </is>
       </c>
     </row>
@@ -810,25 +810,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>@aminaonthemat</t>
+          <t>@tipicokwt</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>aminaonthemat</t>
+          <t>tipicokwt</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>750</v>
+        <v>815</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wild Cotton</t>
+          <t>River</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  19:16</t>
+          <t>2026-05-05  13:54</t>
         </is>
       </c>
     </row>
@@ -838,25 +838,25 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>@kjalabdul</t>
+          <t>@eng_menawer</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>kjalabdul</t>
+          <t>eng_menawer</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>722</v>
+        <v>813</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Linen</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03  21:44</t>
+          <t>2026-05-03  18:52</t>
         </is>
       </c>
     </row>
@@ -866,25 +866,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>@badoraaals</t>
+          <t>@manayel.ahmad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>badoraaals</t>
+          <t>manayel.ahmad</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>697</v>
+        <v>809</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Wild Cotton</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  21:06</t>
+          <t>2026-05-05  15:55</t>
         </is>
       </c>
     </row>
@@ -894,25 +894,25 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>@m_alwazzan88</t>
+          <t>@farahpunzel</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>m_alwazzan88</t>
+          <t>farahpunzel</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>684</v>
+        <v>799</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Linen</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03  22:57</t>
+          <t>2026-05-04  12:23</t>
         </is>
       </c>
     </row>
@@ -922,16 +922,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>@ghazitark</t>
+          <t>@bbritto99</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ghazitark</t>
+          <t>bbritto99</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>627</v>
+        <v>798</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  22:45</t>
+          <t>2026-05-04  00:06</t>
         </is>
       </c>
     </row>
@@ -950,16 +950,16 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>@sonanddark</t>
+          <t>@w1nb</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>sonanddark</t>
+          <t>w1nb</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>590</v>
+        <v>773</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03  18:37</t>
+          <t>2026-05-04  06:05</t>
         </is>
       </c>
     </row>
@@ -978,25 +978,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>@falnaqeeb</t>
+          <t>@haya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>falnaqeeb</t>
+          <t>haya</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>590</v>
+        <v>769</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  20:12</t>
+          <t>2026-05-04  23:02</t>
         </is>
       </c>
     </row>
@@ -1006,16 +1006,16 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>@rydeenn</t>
+          <t>@qemlas</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>rydeenn</t>
+          <t>qemlas</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>516</v>
+        <v>762</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03  18:43</t>
+          <t>2026-05-05  15:38</t>
         </is>
       </c>
     </row>
@@ -1034,25 +1034,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>@aminaxsalim</t>
+          <t>@aminaonthemat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>aminaxsalim</t>
+          <t>aminaonthemat</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>488</v>
+        <v>750</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Wild Cotton</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03  19:13</t>
+          <t>2026-05-03  19:16</t>
         </is>
       </c>
     </row>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>@mfalhaaa</t>
+          <t>@kjalabdul</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>mfalhaaa</t>
+          <t>kjalabdul</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>453</v>
+        <v>722</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Linen</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03  23:27</t>
+          <t>2026-05-03  21:44</t>
         </is>
       </c>
     </row>
@@ -1090,16 +1090,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>@salemalharan</t>
+          <t>@badoraaals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>salemalharan</t>
+          <t>badoraaals</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>442</v>
+        <v>697</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04  02:55</t>
+          <t>2026-05-03  21:06</t>
         </is>
       </c>
     </row>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>@v97o0</t>
+          <t>@m_alwazzan88</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>v97o0</t>
+          <t>m_alwazzan88</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>382</v>
+        <v>684</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Linen</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04  06:03</t>
+          <t>2026-05-03  22:57</t>
         </is>
       </c>
     </row>
@@ -1146,25 +1146,473 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>@ghazitark</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ghazitark</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>627</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  22:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>@jojo_mahmd965</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>jojo_mahmd965</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>593</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05  16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>@sonanddark</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sonanddark</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>590</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03  18:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>@falnaqeeb</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>falnaqeeb</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>590</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>River</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>@has.2002</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>has.2002</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>528</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04  16:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>@rydeenn</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>rydeenn</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>516</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>@haalkharji</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>haalkharji</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>513</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05  03:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>@shalhouli</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>shalhouli</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>511</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04  23:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>@9agerrr</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>9agerrr</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>493</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04  14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>@aminaxsalim</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>aminaxsalim</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  19:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>@lolo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lolo</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>481</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05  16:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>@mfalhaaa</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>mfalhaaa</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>453</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03  23:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>@salemalharan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>salemalharan</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04  02:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>@Elaf_kossale</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>elaf_kossale</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>432</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05  21:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>@v97o0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>v97o0</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>382</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04  06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>@Jaljaiedan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>jaljaiedan</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D40" s="5" t="n">
         <v>359</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Etienne</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026-05-03  20:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>@sa.alabdali</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sa.alabdali</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>253</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Wild Cotton</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05  05:24</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1653,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -1237,7 +1685,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>359</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
@@ -1247,7 +1695,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7">
@@ -1258,7 +1706,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-04  13:42  Kuwait</t>
+          <t>2026-05-05  22:11  Kuwait</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -1291,27 +1739,27 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Linen</t>
+          <t>River</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Linen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
